--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,8 +778,16 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91840985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91840985</v>
+        <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>92044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Stor-Hasslingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464644</v>
+        <v>464921</v>
       </c>
       <c r="R2" t="n">
-        <v>7101439</v>
+        <v>7101293</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,28 +775,1219 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769282</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135769280</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>464999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7101316</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769280</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91840985</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>464644</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7101439</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91840985</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135769273</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465047</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7101313</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769273</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135769275</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465048</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7101313</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769275</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135769276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465025</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7101296</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769276</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135769277</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465015</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7101294</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769277</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135769278</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>465014</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7101298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769278</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135769279</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>465012</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7101305</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769279</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135769281</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>464936</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7101286</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769281</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135769283</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92440</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Hasslingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>464889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7101314</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769283</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135769273</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135769275</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135769276</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135769277</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135769278</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135769279</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135769281</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135769273</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135769275</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135769276</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135769277</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135769278</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135769279</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135769281</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135769273</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135769275</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135769276</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135769277</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135769278</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135769279</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135769281</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135769273</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135769275</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135769276</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135769277</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135769278</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135769279</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135769281</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92466</v>
+        <v>92472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30358-2026 artfynd.xlsx
+++ b/artfynd/A 30358-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135769282</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135769280</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135769273</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>135769275</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135769276</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135769277</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>135769278</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135769279</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135769281</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135769283</v>
       </c>
       <c r="B12" t="n">
-        <v>92472</v>
+        <v>92479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
